--- a/data/trans_camb/IP19C06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Clase-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 10,46</t>
+          <t>1,69; 10,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,62</t>
+          <t>0,67; 4,18</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,31</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,47</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,39</t>
+          <t>0,0; 9,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,85</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,61</t>
         </is>
       </c>
     </row>
@@ -1546,42 +1546,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,75</t>
+          <t>0,0; 5,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 5,69</t>
+          <t>-1,1; 6,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-3,79; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 0,0</t>
+          <t>-3,89; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 2,75</t>
+          <t>-0,46; 2,79</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,93</t>
+          <t>-0,85; 1,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,66</t>
+          <t>-1,35; 0,65</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 12,81</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,84</t>
+          <t>0,0; 9,76</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 0,0</t>
+          <t>-9,62; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 0,0</t>
+          <t>-10,67; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 11,74</t>
+          <t>-3,91; 9,48</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 5,17</t>
+          <t>-1,85; 5,25</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 3,16</t>
+          <t>-1,85; 2,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,54</t>
+          <t>-1,84; 5,14</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,45</t>
+          <t>0,3; 2,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,78</t>
+          <t>0,77; 2,72</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,36</t>
+          <t>-0,53; 1,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 0,0</t>
+          <t>-1,37; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,05</t>
+          <t>-0,53; 1,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,31</t>
+          <t>0,11; 1,34</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,45</t>
+          <t>-0,36; 0,42</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,56</t>
+          <t>0,22; 1,48</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-44,63; —</t>
+          <t>-48,75; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-12,88; —</t>
+          <t>-11,65; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Clase-trans_camb.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,68</t>
+          <t>1,62; 10,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,18</t>
+          <t>0,69; 4,5</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,18</t>
+          <t>0,0; 7,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,75</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 3,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,61</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
     </row>
@@ -1546,42 +1546,42 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 6,67</t>
+          <t>-0,76; 6,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 0,0</t>
+          <t>-3,8; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 0,0</t>
+          <t>-4,29; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 2,79</t>
+          <t>-0,7; 2,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,73</t>
+          <t>-0,84; 1,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,65</t>
+          <t>-1,68; 0,65</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,81</t>
+          <t>0,0; 13,2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,76</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1772,32 +1772,32 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 0,0</t>
+          <t>-8,8; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 0,0</t>
+          <t>-9,64; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 9,48</t>
+          <t>-3,88; 10,77</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 5,25</t>
+          <t>-1,84; 5,0</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,9</t>
+          <t>-1,86; 2,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,14</t>
+          <t>-1,84; 5,41</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,06</t>
+          <t>0,34; 2,22</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,72</t>
+          <t>0,72; 2,74</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,23</t>
+          <t>-0,48; 1,35</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 0,0</t>
+          <t>-1,29; 0,0</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,15</t>
+          <t>-0,51; 1,24</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,34</t>
+          <t>0,09; 1,42</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,42</t>
+          <t>-0,31; 0,41</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,48</t>
+          <t>0,23; 1,46</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-48,75; —</t>
+          <t>-36,69; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-11,65; —</t>
+          <t>-19,18; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C06-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C06-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>4,68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,07</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,97; 10,97</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,5</t>
+          <t>0,67; 4,83</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,24 +840,24 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,37</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,32</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -903,12 +903,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 8,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,83</t>
+          <t>0,0; 6,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
     </row>
@@ -1056,22 +1056,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,07</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 10,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1162,22 +1162,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1272,24 +1272,24 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,77</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,45</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,42</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1,11</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>0,69</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>-0,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,76; 5,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>-3,77; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 6,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 0,0</t>
+          <t>0,0; 6,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 0,0</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,72</t>
+          <t>-0,43; 2,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,76</t>
+          <t>-0,84; 1,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,65</t>
+          <t>-1,28; 0,62</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1594,34 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>189,76%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>189,76%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
           <t>143,79%</t>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-25,26%</t>
+          <t>-30,28%</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-1,94</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>3,19</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>1,89</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-1,94</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>0,0</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>-0,21</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,2</t>
+          <t>-8,35; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,33</t>
+          <t>-9,66; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,34; 2,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-8,8; 0,0</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 0,0</t>
+          <t>0,0; 9,84</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 10,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,0</t>
+          <t>-1,83; 5,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 2,9</t>
+          <t>-2,71; 3,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,41</t>
+          <t>-2,94; 1,44</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-24,71%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>-23,33%</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,29</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,36</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-0,0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>0,96</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,41</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>1,49</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,29</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-0,36</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,76</t>
+          <t>0,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,22</t>
+          <t>-0,55; 1,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>-1,27; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,74</t>
+          <t>-0,82; 0,63</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 1,35</t>
+          <t>0,34; 2,45</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,0</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 1,24</t>
+          <t>0,69; 2,76</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,42</t>
+          <t>0,08; 1,31</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,41</t>
+          <t>-0,31; 0,45</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,46</t>
+          <t>0,16; 1,36</t>
         </is>
       </c>
     </row>
@@ -2026,34 +2026,34 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>81,63%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-1,29%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>81,63%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>39,15%</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
           <t>337,45%</t>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>412,41%</t>
+          <t>369,59%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-36,69; —</t>
+          <t>-44,63; —</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-19,18; —</t>
+          <t>-16,78; —</t>
         </is>
       </c>
     </row>
